--- a/data/trans_camb/Q45B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,15</t>
+          <t>0,28; 2,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,48</t>
+          <t>-0,38; 1,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,35</t>
+          <t>-0,92; 1,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,9</t>
+          <t>-2,73; -0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,43</t>
+          <t>-0,19; 1,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; -0,18</t>
+          <t>-1,46; -0,13</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 621,07</t>
+          <t>8,1; 597,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 411,48</t>
+          <t>-52,26; 419,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 77,32</t>
+          <t>-32,42; 87,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-91,17; -40,11</t>
+          <t>-90,2; -33,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 111,08</t>
+          <t>-11,36; 122,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,45; -6,6</t>
+          <t>-73,71; -8,22</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,43</t>
+          <t>-0,65; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; -0,73</t>
+          <t>-2,38; -0,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 0,19</t>
+          <t>-3,77; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -4,61</t>
+          <t>-8,09; -4,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,44</t>
+          <t>-1,85; 0,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -2,85</t>
+          <t>-4,79; -2,86</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 80,85</t>
+          <t>-23,83; 82,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,37; -38,54</t>
+          <t>-81,77; -36,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 2,24</t>
+          <t>-32,27; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,39; -47,42</t>
+          <t>-68,19; -47,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 7,69</t>
+          <t>-26,74; 7,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,6; -49,93</t>
+          <t>-69,03; -49,7</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,58</t>
+          <t>-2,86; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,55</t>
+          <t>-4,54; -0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,22</t>
+          <t>-2,37; 7,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -4,23</t>
+          <t>-11,14; -3,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,07</t>
+          <t>-1,28; 4,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -2,73</t>
+          <t>-6,74; -2,69</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 93,92</t>
+          <t>-56,72; 92,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-86,79; -15,75</t>
+          <t>-85,87; -17,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 63,47</t>
+          <t>-15,06; 68,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -35,43</t>
+          <t>-71,95; -33,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 57,52</t>
+          <t>-13,72; 59,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,84; -37,67</t>
+          <t>-70,22; -37,98</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,25</t>
+          <t>-0,31; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; -0,49</t>
+          <t>-1,67; -0,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,88</t>
+          <t>-1,72; 0,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; -3,19</t>
+          <t>-5,59; -3,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,84</t>
+          <t>-0,69; 0,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -2,04</t>
+          <t>-3,36; -1,99</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 74,49</t>
+          <t>-13,46; 75,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,73; -29,06</t>
+          <t>-69,13; -26,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 11,9</t>
+          <t>-20,07; 12,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-63,84; -45,07</t>
+          <t>-64,4; -43,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 18,46</t>
+          <t>-13,06; 19,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,89; -45,2</t>
+          <t>-63,02; -44,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Q45B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/Q45B_R-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,21</t>
+          <t>0,2; 2,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,33</t>
+          <t>-0,31; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,47</t>
+          <t>-1,08; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,73</t>
+          <t>-2,78; -0,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,43</t>
+          <t>-0,25; 1,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,13</t>
+          <t>-1,39; -0,08</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 597,87</t>
+          <t>-0,65; 565,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 419,57</t>
+          <t>-47,38; 468,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 87,86</t>
+          <t>-37,54; 78,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-90,2; -33,25</t>
+          <t>-91,13; -40,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 122,1</t>
+          <t>-12,78; 106,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,71; -8,22</t>
+          <t>-72,55; -0,75</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,39</t>
+          <t>-0,85; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,65</t>
+          <t>-2,42; -0,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,25</t>
+          <t>-3,74; 0,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -4,58</t>
+          <t>-8,2; -4,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,42</t>
+          <t>-1,85; 0,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; -2,86</t>
+          <t>-4,84; -2,93</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 82,03</t>
+          <t>-30,4; 74,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,77; -36,56</t>
+          <t>-81,43; -33,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 2,61</t>
+          <t>-31,71; 3,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,19; -47,56</t>
+          <t>-68,71; -47,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 7,41</t>
+          <t>-26,63; 8,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-69,03; -49,7</t>
+          <t>-68,99; -50,53</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,4</t>
+          <t>-2,56; 2,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; -0,57</t>
+          <t>-4,6; -0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,5</t>
+          <t>-2,01; 7,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -3,75</t>
+          <t>-11,16; -3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,31</t>
+          <t>-1,1; 4,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -2,69</t>
+          <t>-6,73; -2,73</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,72; 92,26</t>
+          <t>-52,74; 104,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-85,87; -17,24</t>
+          <t>-85,47; -16,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 68,72</t>
+          <t>-14,39; 67,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,95; -33,04</t>
+          <t>-70,65; -30,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 59,91</t>
+          <t>-12,68; 59,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,22; -37,98</t>
+          <t>-70,12; -38,11</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,27</t>
+          <t>-0,28; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; -0,46</t>
+          <t>-1,71; -0,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,93</t>
+          <t>-1,6; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -3,11</t>
+          <t>-5,4; -3,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,88</t>
+          <t>-0,74; 0,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -1,99</t>
+          <t>-3,36; -2,11</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 75,37</t>
+          <t>-12,11; 71,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,13; -26,26</t>
+          <t>-69,5; -28,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 12,96</t>
+          <t>-18,72; 13,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,4; -43,65</t>
+          <t>-63,49; -45,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 19,1</t>
+          <t>-13,6; 17,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,02; -44,29</t>
+          <t>-62,48; -45,98</t>
         </is>
       </c>
     </row>
